--- a/Design_files/Control_Board/BOM/Client BOM.xlsx
+++ b/Design_files/Control_Board/BOM/Client BOM.xlsx
@@ -1,16 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\eSpark-Consultants\elijahkorp-controlproject\Design_files\Control_Board\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF13EE2F-96FE-4F26-A620-4E71710C752C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9144" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
     <sheet name="10 Boards" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -308,7 +325,7 @@
     <t>J11</t>
   </si>
   <si>
-    <t>1x4P 1 2mm Male pin 4 -25℃~+85℃ 2A Surface Mount SMD,P=2mm Wire To Board / Wire To Wire Connector ROHS
+    <t>1x4P 1 2mm Male pin 4 -25℃~+85℃ 2A Surface Mount SMD,P=2mm Wire To Board / Wire To Wire Connector ROHS_x000D_
 C3029442</t>
   </si>
   <si>
@@ -606,15 +623,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="5">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -750,147 +763,10 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -915,194 +791,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="27">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1310,253 +1000,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1588,15 +1039,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1627,7 +1072,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="178" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1696,44 +1141,17 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -1741,84 +1159,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="0003A4CB"/>
-      <color rgb="002CD0B2"/>
+      <color rgb="FF03A4CB"/>
+      <color rgb="FF2CD0B2"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
@@ -1834,13 +1218,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1868,7 +1258,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
@@ -1877,20 +1267,26 @@
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1905000</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171707</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2169,27 +1565,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="3.13888888888889" style="69" customWidth="1"/>
-    <col min="3" max="3" width="18.712962962963" style="69" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="57" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="57" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="29.3333333333333" customWidth="1"/>
-    <col min="7" max="7" width="26.4444444444444" customWidth="1"/>
-    <col min="8" max="8" width="18.1111111111111" customWidth="1"/>
-    <col min="9" max="9" width="7.33333333333333" customWidth="1"/>
+    <col min="6" max="6" width="29.28515625" customWidth="1"/>
+    <col min="7" max="7" width="26.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="8.88888888888889" customWidth="1"/>
-    <col min="13" max="13" width="29.4259259259259" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" customWidth="1"/>
+    <col min="13" max="13" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -2201,13 +1598,13 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-    </row>
-    <row r="2" ht="31.95" spans="1:13">
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+    </row>
+    <row r="2" spans="1:13" ht="31.5">
       <c r="A2" s="2"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -2215,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="7"/>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="58" t="s">
         <v>1</v>
       </c>
       <c r="G2" s="8"/>
@@ -2223,8 +1620,8 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="55"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="51"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="2"/>
@@ -2234,16 +1631,16 @@
         <v>2</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="59" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="12"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="56"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="62"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2"/>
@@ -2253,16 +1650,16 @@
         <v>4</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="58"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="63"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2"/>
@@ -2272,1468 +1669,1468 @@
         <v>5</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="72" t="s">
+      <c r="F5" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="58"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="63"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="58"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="63"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="58"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="63"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="58"/>
-    </row>
-    <row r="9" ht="15.15" spans="1:13">
+      <c r="B8" s="27"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="63"/>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="2"/>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="33" t="s">
+      <c r="H9" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="34" t="s">
+      <c r="I9" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="60" t="s">
+      <c r="K9" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="61" t="s">
+      <c r="L9" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="33" t="s">
+      <c r="M9" s="31" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="24.75" spans="1:13">
+    <row r="10" spans="1:13" ht="24">
       <c r="A10" s="2"/>
-      <c r="B10" s="36">
+      <c r="B10" s="34">
         <f t="shared" ref="B10:B41" si="0">ROW(B10)-ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="39" t="s">
+      <c r="G10" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="38" t="s">
+      <c r="H10" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="39" t="s">
+      <c r="I10" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="38">
+      <c r="J10" s="36">
         <v>8</v>
       </c>
-      <c r="K10" s="39">
+      <c r="K10" s="37">
         <f t="shared" ref="K10:K41" si="1">J10*5</f>
         <v>40</v>
       </c>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-    </row>
-    <row r="11" ht="15.15" spans="1:13">
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="2"/>
-      <c r="B11" s="36">
+      <c r="B11" s="34">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="41" t="s">
+      <c r="G11" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="41" t="s">
+      <c r="I11" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="40">
+      <c r="J11" s="38">
         <v>2</v>
       </c>
-      <c r="K11" s="41">
+      <c r="K11" s="39">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-    </row>
-    <row r="12" ht="24.75" spans="1:13">
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+    </row>
+    <row r="12" spans="1:13" ht="36">
       <c r="A12" s="2"/>
-      <c r="B12" s="36">
+      <c r="B12" s="34">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="39" t="s">
+      <c r="G12" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="38" t="s">
+      <c r="H12" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="39" t="s">
+      <c r="I12" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="38">
-        <v>1</v>
-      </c>
-      <c r="K12" s="39">
+      <c r="J12" s="36">
+        <v>1</v>
+      </c>
+      <c r="K12" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-    </row>
-    <row r="13" ht="15.15" spans="1:13">
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="2"/>
-      <c r="B13" s="36">
+      <c r="B13" s="34">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="41" t="s">
+      <c r="G13" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="40" t="s">
+      <c r="H13" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="38">
         <v>2</v>
       </c>
-      <c r="K13" s="41">
+      <c r="K13" s="39">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-    </row>
-    <row r="14" ht="15.15" spans="1:13">
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="2"/>
-      <c r="B14" s="36">
+      <c r="B14" s="34">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="39" t="s">
+      <c r="G14" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="38" t="s">
+      <c r="H14" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="I14" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="J14" s="38">
+      <c r="J14" s="36">
         <v>2</v>
       </c>
-      <c r="K14" s="39">
+      <c r="K14" s="37">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-    </row>
-    <row r="15" ht="24.75" spans="1:13">
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
+    </row>
+    <row r="15" spans="1:13" ht="36">
       <c r="A15" s="2"/>
-      <c r="B15" s="36">
+      <c r="B15" s="34">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="41" t="s">
+      <c r="G15" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="40" t="s">
+      <c r="H15" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="I15" s="41" t="s">
+      <c r="I15" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="J15" s="40">
-        <v>1</v>
-      </c>
-      <c r="K15" s="41">
+      <c r="J15" s="38">
+        <v>1</v>
+      </c>
+      <c r="K15" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-    </row>
-    <row r="16" ht="15.15" spans="1:13">
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="2"/>
-      <c r="B16" s="36">
+      <c r="B16" s="34">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="38" t="s">
+      <c r="F16" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="39" t="s">
+      <c r="G16" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="38" t="s">
+      <c r="H16" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="I16" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J16" s="38">
-        <v>1</v>
-      </c>
-      <c r="K16" s="39">
+      <c r="I16" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J16" s="36">
+        <v>1</v>
+      </c>
+      <c r="K16" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-    </row>
-    <row r="17" ht="36.75" spans="1:13">
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+    </row>
+    <row r="17" spans="1:13" ht="36">
       <c r="A17" s="2"/>
-      <c r="B17" s="36">
+      <c r="B17" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="40" t="s">
+      <c r="H17" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="I17" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J17" s="40">
-        <v>1</v>
-      </c>
-      <c r="K17" s="41">
+      <c r="I17" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J17" s="38">
+        <v>1</v>
+      </c>
+      <c r="K17" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-    </row>
-    <row r="18" ht="15.15" spans="1:13">
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="2"/>
-      <c r="B18" s="36">
+      <c r="B18" s="34">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="G18" s="39" t="s">
+      <c r="G18" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="H18" s="38" t="s">
+      <c r="H18" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="I18" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J18" s="38">
-        <v>1</v>
-      </c>
-      <c r="K18" s="39">
+      <c r="I18" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" s="36">
+        <v>1</v>
+      </c>
+      <c r="K18" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-    </row>
-    <row r="19" ht="15.15" spans="1:13">
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="2"/>
-      <c r="B19" s="36">
+      <c r="B19" s="34">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="41" t="s">
+      <c r="E19" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="41" t="s">
+      <c r="G19" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="H19" s="40" t="s">
+      <c r="H19" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="I19" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J19" s="40">
-        <v>1</v>
-      </c>
-      <c r="K19" s="41">
+      <c r="I19" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" s="38">
+        <v>1</v>
+      </c>
+      <c r="K19" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-    </row>
-    <row r="20" ht="48.75" spans="1:13">
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+    </row>
+    <row r="20" spans="1:13" ht="48">
       <c r="A20" s="2"/>
-      <c r="B20" s="36">
+      <c r="B20" s="34">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="38" t="s">
+      <c r="F20" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="38" t="s">
+      <c r="H20" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="I20" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J20" s="38">
+      <c r="I20" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="36">
         <v>3</v>
       </c>
-      <c r="K20" s="39">
+      <c r="K20" s="37">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-    </row>
-    <row r="21" ht="36.75" spans="1:13">
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+    </row>
+    <row r="21" spans="1:13" ht="48">
       <c r="A21" s="2"/>
-      <c r="B21" s="36">
+      <c r="B21" s="34">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="D21" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="38" t="s">
+      <c r="F21" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="H21" s="40" t="s">
+      <c r="H21" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="I21" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J21" s="40">
-        <v>1</v>
-      </c>
-      <c r="K21" s="41">
+      <c r="I21" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J21" s="38">
+        <v>1</v>
+      </c>
+      <c r="K21" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-    </row>
-    <row r="22" ht="24.75" spans="1:13">
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+    </row>
+    <row r="22" spans="1:13" ht="24">
       <c r="A22" s="2"/>
-      <c r="B22" s="36">
+      <c r="B22" s="34">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="E22" s="39" t="s">
+      <c r="E22" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="F22" s="38" t="s">
+      <c r="F22" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="G22" s="39" t="s">
+      <c r="G22" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H22" s="38" t="s">
+      <c r="H22" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I22" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J22" s="38">
+      <c r="I22" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J22" s="36">
         <v>2</v>
       </c>
-      <c r="K22" s="39">
+      <c r="K22" s="37">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-    </row>
-    <row r="23" ht="15.15" spans="1:13">
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="2"/>
-      <c r="B23" s="36">
+      <c r="B23" s="34">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="41" t="s">
+      <c r="E23" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="F23" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="G23" s="41" t="s">
+      <c r="G23" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="H23" s="40"/>
-      <c r="I23" s="41" t="s">
+      <c r="H23" s="38"/>
+      <c r="I23" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="J23" s="40">
+      <c r="J23" s="38">
         <v>5</v>
       </c>
-      <c r="K23" s="41">
+      <c r="K23" s="39">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="L23" s="40"/>
-      <c r="M23" s="40"/>
-    </row>
-    <row r="24" ht="48.75" spans="1:13">
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+    </row>
+    <row r="24" spans="1:13" ht="60">
       <c r="A24" s="2"/>
-      <c r="B24" s="36">
+      <c r="B24" s="34">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="E24" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="38" t="s">
+      <c r="F24" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G24" s="38" t="s">
+      <c r="G24" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="H24" s="38" t="s">
+      <c r="H24" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="I24" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J24" s="38">
-        <v>1</v>
-      </c>
-      <c r="K24" s="39">
+      <c r="I24" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24" s="36">
+        <v>1</v>
+      </c>
+      <c r="K24" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-    </row>
-    <row r="25" ht="24.75" spans="1:13">
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+    </row>
+    <row r="25" spans="1:13" ht="24">
       <c r="A25" s="2"/>
-      <c r="B25" s="36">
+      <c r="B25" s="34">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="40" t="s">
+      <c r="D25" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="E25" s="41" t="s">
+      <c r="E25" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="F25" s="38" t="s">
+      <c r="F25" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G25" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="H25" s="40" t="s">
+      <c r="H25" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="I25" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J25" s="40">
-        <v>1</v>
-      </c>
-      <c r="K25" s="41">
+      <c r="I25" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J25" s="38">
+        <v>1</v>
+      </c>
+      <c r="K25" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L25" s="40"/>
-      <c r="M25" s="40"/>
-    </row>
-    <row r="26" ht="24.75" spans="1:13">
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+    </row>
+    <row r="26" spans="1:13" ht="36">
       <c r="A26" s="2"/>
-      <c r="B26" s="36">
+      <c r="B26" s="34">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="E26" s="39" t="s">
+      <c r="E26" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G26" s="39" t="s">
+      <c r="G26" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="H26" s="38" t="s">
+      <c r="H26" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="I26" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J26" s="38">
+      <c r="I26" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J26" s="36">
         <v>2</v>
       </c>
-      <c r="K26" s="39">
+      <c r="K26" s="37">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L26" s="38"/>
-      <c r="M26" s="38"/>
-    </row>
-    <row r="27" ht="48.75" spans="1:13">
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
+    </row>
+    <row r="27" spans="1:13" ht="48">
       <c r="A27" s="2"/>
-      <c r="B27" s="36">
+      <c r="B27" s="34">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="40" t="s">
+      <c r="D27" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="41" t="s">
+      <c r="E27" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="40" t="s">
+      <c r="F27" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="G27" s="41" t="s">
+      <c r="G27" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="H27" s="40" t="s">
+      <c r="H27" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="I27" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J27" s="40">
-        <v>1</v>
-      </c>
-      <c r="K27" s="41">
+      <c r="I27" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J27" s="38">
+        <v>1</v>
+      </c>
+      <c r="K27" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L27" s="40"/>
-      <c r="M27" s="40"/>
-    </row>
-    <row r="28" ht="15.15" spans="1:13">
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="2"/>
-      <c r="B28" s="36">
+      <c r="B28" s="34">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="D28" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="39" t="s">
+      <c r="E28" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="F28" s="38" t="s">
+      <c r="F28" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G28" s="38" t="s">
+      <c r="G28" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="H28" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="I28" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J28" s="38">
+      <c r="H28" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J28" s="36">
         <v>3</v>
       </c>
-      <c r="K28" s="39">
+      <c r="K28" s="37">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="L28" s="38"/>
-      <c r="M28" s="38"/>
-    </row>
-    <row r="29" ht="36.75" spans="1:13">
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
+    </row>
+    <row r="29" spans="1:13" ht="36">
       <c r="A29" s="2"/>
-      <c r="B29" s="36">
+      <c r="B29" s="34">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C29" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D29" s="40" t="s">
+      <c r="D29" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="E29" s="41" t="s">
+      <c r="E29" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="F29" s="40" t="s">
+      <c r="F29" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="G29" s="41" t="s">
+      <c r="G29" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="H29" s="40" t="s">
+      <c r="H29" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="I29" s="41" t="s">
+      <c r="I29" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="J29" s="40">
+      <c r="J29" s="38">
         <v>2</v>
       </c>
-      <c r="K29" s="41">
+      <c r="K29" s="39">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
-    </row>
-    <row r="30" ht="36.75" spans="1:13">
+      <c r="L29" s="38"/>
+      <c r="M29" s="38"/>
+    </row>
+    <row r="30" spans="1:13" ht="36">
       <c r="A30" s="2"/>
-      <c r="B30" s="36">
+      <c r="B30" s="34">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="37" t="s">
+      <c r="C30" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="E30" s="39" t="s">
+      <c r="E30" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="F30" s="38" t="s">
+      <c r="F30" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="G30" s="39" t="s">
+      <c r="G30" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="H30" s="38" t="s">
+      <c r="H30" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="I30" s="39" t="s">
+      <c r="I30" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="J30" s="38">
-        <v>1</v>
-      </c>
-      <c r="K30" s="39">
+      <c r="J30" s="36">
+        <v>1</v>
+      </c>
+      <c r="K30" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L30" s="38"/>
-      <c r="M30" s="38"/>
-    </row>
-    <row r="31" ht="15.15" spans="1:13">
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="2"/>
-      <c r="B31" s="36">
+      <c r="B31" s="34">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="42" t="s">
+      <c r="C31" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D31" s="40" t="s">
+      <c r="D31" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="E31" s="41" t="s">
+      <c r="E31" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="40" t="s">
+      <c r="F31" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="G31" s="41" t="s">
+      <c r="G31" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="H31" s="40" t="s">
+      <c r="H31" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="41" t="s">
+      <c r="I31" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="J31" s="40">
+      <c r="J31" s="38">
         <v>7</v>
       </c>
-      <c r="K31" s="41">
+      <c r="K31" s="39">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="L31" s="40"/>
-      <c r="M31" s="40"/>
-    </row>
-    <row r="32" ht="36.75" spans="1:13">
+      <c r="L31" s="38"/>
+      <c r="M31" s="38"/>
+    </row>
+    <row r="32" spans="1:13" ht="36">
       <c r="A32" s="2"/>
-      <c r="B32" s="36">
+      <c r="B32" s="34">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="42" t="s">
+      <c r="C32" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D32" s="38" t="s">
+      <c r="D32" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="E32" s="39" t="s">
+      <c r="E32" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="F32" s="38" t="s">
+      <c r="F32" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="G32" s="39" t="s">
+      <c r="G32" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="H32" s="38" t="s">
+      <c r="H32" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="I32" s="39" t="s">
+      <c r="I32" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="J32" s="38">
-        <v>1</v>
-      </c>
-      <c r="K32" s="39">
+      <c r="J32" s="36">
+        <v>1</v>
+      </c>
+      <c r="K32" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L32" s="38"/>
-      <c r="M32" s="38"/>
-    </row>
-    <row r="33" ht="15.15" spans="1:13">
+      <c r="L32" s="36"/>
+      <c r="M32" s="36"/>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="2"/>
-      <c r="B33" s="36">
+      <c r="B33" s="34">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="42" t="s">
+      <c r="C33" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="40" t="s">
+      <c r="D33" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="E33" s="41" t="s">
+      <c r="E33" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="F33" s="40" t="s">
+      <c r="F33" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="G33" s="41" t="s">
+      <c r="G33" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="H33" s="40" t="s">
+      <c r="H33" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I33" s="41" t="s">
+      <c r="I33" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="J33" s="40">
-        <v>1</v>
-      </c>
-      <c r="K33" s="41">
+      <c r="J33" s="38">
+        <v>1</v>
+      </c>
+      <c r="K33" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L33" s="40"/>
-      <c r="M33" s="40"/>
-    </row>
-    <row r="34" ht="36.75" spans="1:13">
+      <c r="L33" s="38"/>
+      <c r="M33" s="38"/>
+    </row>
+    <row r="34" spans="1:13" ht="36">
       <c r="A34" s="2"/>
-      <c r="B34" s="36">
+      <c r="B34" s="34">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="37" t="s">
+      <c r="C34" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="38" t="s">
+      <c r="D34" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="39" t="s">
+      <c r="E34" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="F34" s="38" t="s">
+      <c r="F34" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="G34" s="39" t="s">
+      <c r="G34" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="H34" s="38" t="s">
+      <c r="H34" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="I34" s="39" t="s">
+      <c r="I34" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="J34" s="38">
-        <v>1</v>
-      </c>
-      <c r="K34" s="39">
+      <c r="J34" s="36">
+        <v>1</v>
+      </c>
+      <c r="K34" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L34" s="38"/>
-      <c r="M34" s="38"/>
-    </row>
-    <row r="35" ht="15.15" spans="1:13">
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="2"/>
-      <c r="B35" s="36">
+      <c r="B35" s="34">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="42" t="s">
+      <c r="C35" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="40" t="s">
+      <c r="D35" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="E35" s="41" t="s">
+      <c r="E35" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="F35" s="40" t="s">
+      <c r="F35" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="G35" s="41" t="s">
+      <c r="G35" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="H35" s="40" t="s">
+      <c r="H35" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I35" s="41" t="s">
+      <c r="I35" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="J35" s="40">
+      <c r="J35" s="38">
         <v>5</v>
       </c>
-      <c r="K35" s="41">
+      <c r="K35" s="39">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="L35" s="40"/>
-      <c r="M35" s="40"/>
-    </row>
-    <row r="36" ht="15.15" spans="1:13">
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="2"/>
-      <c r="B36" s="36">
+      <c r="B36" s="34">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="37" t="s">
+      <c r="C36" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="D36" s="38" t="s">
+      <c r="D36" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="E36" s="39" t="s">
+      <c r="E36" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="F36" s="38" t="s">
+      <c r="F36" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G36" s="39" t="s">
+      <c r="G36" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="H36" s="38" t="s">
+      <c r="H36" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="I36" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J36" s="38">
-        <v>1</v>
-      </c>
-      <c r="K36" s="39">
+      <c r="I36" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J36" s="36">
+        <v>1</v>
+      </c>
+      <c r="K36" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L36" s="38"/>
-      <c r="M36" s="38"/>
-    </row>
-    <row r="37" ht="15.15" spans="1:13">
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="2"/>
-      <c r="B37" s="36">
+      <c r="B37" s="34">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D37" s="40" t="s">
+      <c r="D37" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="E37" s="41" t="s">
+      <c r="E37" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="F37" s="40" t="s">
+      <c r="F37" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="G37" s="41" t="s">
+      <c r="G37" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="H37" s="40" t="s">
+      <c r="H37" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="I37" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J37" s="40">
-        <v>1</v>
-      </c>
-      <c r="K37" s="41">
+      <c r="I37" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J37" s="38">
+        <v>1</v>
+      </c>
+      <c r="K37" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L37" s="40"/>
-      <c r="M37" s="40"/>
-    </row>
-    <row r="38" ht="24.75" spans="1:13">
+      <c r="L37" s="38"/>
+      <c r="M37" s="38"/>
+    </row>
+    <row r="38" spans="1:13" ht="24">
       <c r="A38" s="2"/>
-      <c r="B38" s="36">
+      <c r="B38" s="34">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="37" t="s">
+      <c r="C38" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D38" s="38" t="s">
+      <c r="D38" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="E38" s="39" t="s">
+      <c r="E38" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="F38" s="38" t="s">
+      <c r="F38" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="G38" s="39" t="s">
+      <c r="G38" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="H38" s="38" t="s">
+      <c r="H38" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="I38" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J38" s="38">
-        <v>1</v>
-      </c>
-      <c r="K38" s="39">
+      <c r="I38" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J38" s="36">
+        <v>1</v>
+      </c>
+      <c r="K38" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L38" s="38"/>
-      <c r="M38" s="38"/>
-    </row>
-    <row r="39" ht="36.75" spans="1:13">
+      <c r="L38" s="36"/>
+      <c r="M38" s="36"/>
+    </row>
+    <row r="39" spans="1:13" ht="36">
       <c r="A39" s="2"/>
-      <c r="B39" s="36">
+      <c r="B39" s="34">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="37" t="s">
+      <c r="C39" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D39" s="40" t="s">
+      <c r="D39" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="E39" s="41" t="s">
+      <c r="E39" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="F39" s="40" t="s">
+      <c r="F39" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="G39" s="41" t="s">
+      <c r="G39" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="H39" s="40" t="s">
+      <c r="H39" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="I39" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J39" s="40">
-        <v>1</v>
-      </c>
-      <c r="K39" s="41">
+      <c r="I39" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J39" s="38">
+        <v>1</v>
+      </c>
+      <c r="K39" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L39" s="40"/>
-      <c r="M39" s="40"/>
-    </row>
-    <row r="40" ht="15.15" spans="1:13">
+      <c r="L39" s="38"/>
+      <c r="M39" s="38"/>
+    </row>
+    <row r="40" spans="1:13" ht="24">
       <c r="A40" s="2"/>
-      <c r="B40" s="36">
+      <c r="B40" s="34">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="37" t="s">
+      <c r="C40" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="36" t="s">
         <v>172</v>
       </c>
-      <c r="E40" s="39" t="s">
+      <c r="E40" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="F40" s="38" t="s">
+      <c r="F40" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G40" s="38" t="s">
+      <c r="G40" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="H40" s="38" t="s">
+      <c r="H40" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="I40" s="39" t="s">
+      <c r="I40" s="37" t="s">
         <v>176</v>
       </c>
-      <c r="J40" s="38">
-        <v>1</v>
-      </c>
-      <c r="K40" s="39">
+      <c r="J40" s="36">
+        <v>1</v>
+      </c>
+      <c r="K40" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L40" s="38"/>
-      <c r="M40" s="38"/>
-    </row>
-    <row r="41" ht="24.75" spans="1:13">
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
+    </row>
+    <row r="41" spans="1:13" ht="24">
       <c r="A41" s="2"/>
-      <c r="B41" s="36">
+      <c r="B41" s="34">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="42" t="s">
+      <c r="C41" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="D41" s="40" t="s">
+      <c r="D41" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="E41" s="41" t="s">
+      <c r="E41" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="F41" s="38" t="s">
+      <c r="F41" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G41" s="40" t="s">
+      <c r="G41" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="H41" s="40" t="s">
+      <c r="H41" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="I41" s="41" t="s">
+      <c r="I41" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="J41" s="40">
-        <v>1</v>
-      </c>
-      <c r="K41" s="41">
+      <c r="J41" s="38">
+        <v>1</v>
+      </c>
+      <c r="K41" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L41" s="40"/>
-      <c r="M41" s="40"/>
-    </row>
-    <row r="42" ht="36.75" spans="1:13">
+      <c r="L41" s="38"/>
+      <c r="M41" s="38"/>
+    </row>
+    <row r="42" spans="1:13" ht="48">
       <c r="A42" s="2"/>
-      <c r="B42" s="36">
+      <c r="B42" s="34">
         <f>ROW(B42)-ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="42" t="s">
+      <c r="C42" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="D42" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="E42" s="41" t="s">
+      <c r="D42" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="F42" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G42" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="H42" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="I42" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="J42" s="40">
-        <v>1</v>
-      </c>
-      <c r="K42" s="41">
+      <c r="F42" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G42" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="H42" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I42" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="J42" s="38">
+        <v>1</v>
+      </c>
+      <c r="K42" s="39">
         <f>J42*5</f>
         <v>5</v>
       </c>
-      <c r="L42" s="64" t="s">
+      <c r="L42" s="54" t="s">
         <v>184</v>
       </c>
-      <c r="M42" s="40"/>
-    </row>
-    <row r="43" ht="15.15" spans="1:13">
+      <c r="M42" s="38"/>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="2"/>
-      <c r="B43" s="36">
+      <c r="B43" s="34">
         <f>ROW(B43)-ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="C43" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="D43" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" s="41" t="s">
+      <c r="D43" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="F43" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G43" s="40" t="s">
+      <c r="F43" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="H43" s="40" t="s">
+      <c r="H43" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="I43" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="J43" s="40">
-        <v>1</v>
-      </c>
-      <c r="K43" s="41">
+      <c r="I43" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="J43" s="38">
+        <v>1</v>
+      </c>
+      <c r="K43" s="39">
         <f>J43*5</f>
         <v>5</v>
       </c>
-      <c r="L43" s="64" t="s">
+      <c r="L43" s="54" t="s">
         <v>188</v>
       </c>
-      <c r="M43" s="40"/>
-    </row>
-    <row r="44" ht="15.15" spans="1:13">
+      <c r="M43" s="38"/>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="2"/>
-      <c r="B44" s="36">
+      <c r="B44" s="34">
         <f>ROW(B44)-ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="42" t="s">
+      <c r="C44" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="D44" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="41" t="s">
+      <c r="D44" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E44" s="39" t="s">
         <v>189</v>
       </c>
-      <c r="F44" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G44" s="40" t="s">
+      <c r="F44" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G44" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="H44" s="40" t="s">
+      <c r="H44" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="I44" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="J44" s="40">
-        <v>1</v>
-      </c>
-      <c r="K44" s="41">
+      <c r="I44" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="J44" s="38">
+        <v>1</v>
+      </c>
+      <c r="K44" s="39">
         <f>J44*5</f>
         <v>5</v>
       </c>
-      <c r="L44" s="64" t="s">
+      <c r="L44" s="54" t="s">
         <v>188</v>
       </c>
-      <c r="M44" s="40"/>
-    </row>
-    <row r="45" ht="48.75" spans="1:13">
+      <c r="M44" s="38"/>
+    </row>
+    <row r="45" spans="1:13" ht="48">
       <c r="A45" s="2"/>
-      <c r="B45" s="36">
+      <c r="B45" s="34">
         <f>ROW(B45)-ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="D45" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="E45" s="41" t="s">
+      <c r="D45" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E45" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="F45" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G45" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="H45" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="I45" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="J45" s="40">
-        <v>1</v>
-      </c>
-      <c r="K45" s="41">
+      <c r="F45" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G45" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="H45" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I45" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="J45" s="38">
+        <v>1</v>
+      </c>
+      <c r="K45" s="39">
         <f>J45*5</f>
         <v>5</v>
       </c>
-      <c r="L45" s="64" t="s">
+      <c r="L45" s="54" t="s">
         <v>184</v>
       </c>
-      <c r="M45" s="40"/>
+      <c r="M45" s="38"/>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="2"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="47"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="48"/>
-      <c r="K46" s="48"/>
-      <c r="L46" s="65"/>
-      <c r="M46" s="66"/>
-    </row>
-    <row r="47" ht="14.55" spans="1:13">
+      <c r="B46" s="41"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="46"/>
+      <c r="K46" s="46"/>
+      <c r="L46" s="46"/>
+      <c r="M46" s="55"/>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="2"/>
-      <c r="B47" s="49"/>
-      <c r="C47" s="50"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="52"/>
-      <c r="H47" s="52"/>
-      <c r="I47" s="52"/>
-      <c r="J47" s="52"/>
-      <c r="K47" s="52"/>
-      <c r="L47" s="67"/>
-      <c r="M47" s="68"/>
+      <c r="B47" s="47"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="50"/>
+      <c r="G47" s="50"/>
+      <c r="H47" s="50"/>
+      <c r="I47" s="50"/>
+      <c r="J47" s="50"/>
+      <c r="K47" s="50"/>
+      <c r="L47" s="50"/>
+      <c r="M47" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3741,38 +3138,36 @@
     <mergeCell ref="M3:M8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L42" r:id="rId2" display="Aliexpress"/>
-    <hyperlink ref="L43" r:id="rId3" display="LCSC"/>
-    <hyperlink ref="L44" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="L45" r:id="rId5" display="Aliexpress"/>
+    <hyperlink ref="L42" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="L43" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="L44" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="L45" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M47"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="3.66666666666667" customWidth="1"/>
-    <col min="3" max="3" width="14.4444444444444" customWidth="1"/>
-    <col min="4" max="4" width="33.1111111111111" customWidth="1"/>
-    <col min="5" max="5" width="30.8888888888889" customWidth="1"/>
-    <col min="6" max="6" width="28.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="26.4444444444444" customWidth="1"/>
-    <col min="8" max="8" width="13.7777777777778" customWidth="1"/>
-    <col min="9" max="9" width="7.33333333333333" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="33.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="6" max="6" width="28.85546875" customWidth="1"/>
+    <col min="7" max="7" width="26.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="12" width="20.1111111111111" customWidth="1"/>
-    <col min="13" max="13" width="28.2222222222222" customWidth="1"/>
+    <col min="11" max="12" width="20.140625" customWidth="1"/>
+    <col min="13" max="13" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.15" spans="1:13">
+    <row r="1" spans="1:13">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3781,13 +3176,13 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-    </row>
-    <row r="2" ht="31.95" spans="1:13">
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+    </row>
+    <row r="2" spans="1:13" ht="31.5">
       <c r="A2" s="2"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -3795,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="7"/>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="58" t="s">
         <v>1</v>
       </c>
       <c r="G2" s="8"/>
@@ -3803,8 +3198,8 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="55"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="51"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="2"/>
@@ -3814,16 +3209,16 @@
         <v>2</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="59" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="12"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="56"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="62"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2"/>
@@ -3833,16 +3228,16 @@
         <v>4</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="58"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="63"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2"/>
@@ -3852,1470 +3247,1470 @@
         <v>5</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="72" t="s">
+      <c r="F5" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="58"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="63"/>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="58"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="63"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="58"/>
-    </row>
-    <row r="8" ht="15.15" spans="1:13">
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="63"/>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="2"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="58"/>
-    </row>
-    <row r="9" ht="15.15" spans="1:13">
+      <c r="B8" s="27"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="63"/>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="2"/>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="34" t="s">
+      <c r="G9" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="33" t="s">
+      <c r="H9" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="34" t="s">
+      <c r="I9" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="33" t="s">
+      <c r="J9" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="60" t="s">
+      <c r="K9" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="61" t="s">
+      <c r="L9" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="M9" s="33" t="s">
+      <c r="M9" s="31" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="24.75" spans="1:13">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36">
+    <row r="10" spans="1:13" s="1" customFormat="1" ht="24">
+      <c r="A10" s="33"/>
+      <c r="B10" s="34">
         <f t="shared" ref="B10:B45" si="0">ROW(B10)-ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="39" t="s">
+      <c r="G10" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="38" t="s">
+      <c r="H10" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="39" t="s">
+      <c r="I10" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="38">
+      <c r="J10" s="36">
         <v>8</v>
       </c>
-      <c r="K10" s="38">
+      <c r="K10" s="36">
         <f>J10*10</f>
         <v>80</v>
       </c>
-      <c r="L10" s="62"/>
-      <c r="M10" s="38"/>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A11" s="35"/>
-      <c r="B11" s="36">
+      <c r="L10" s="37"/>
+      <c r="M10" s="36"/>
+    </row>
+    <row r="11" spans="1:13" s="1" customFormat="1">
+      <c r="A11" s="33"/>
+      <c r="B11" s="34">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="41" t="s">
+      <c r="G11" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="41" t="s">
+      <c r="I11" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="40">
+      <c r="J11" s="38">
         <v>2</v>
       </c>
-      <c r="K11" s="40">
-        <f t="shared" ref="K11:K41" si="1">J11*10</f>
+      <c r="K11" s="38">
+        <f t="shared" ref="K11:K45" si="1">J11*10</f>
         <v>20</v>
       </c>
-      <c r="L11" s="63"/>
-      <c r="M11" s="40"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="24.75" spans="1:13">
-      <c r="A12" s="35"/>
-      <c r="B12" s="36">
+      <c r="L11" s="37"/>
+      <c r="M11" s="38"/>
+    </row>
+    <row r="12" spans="1:13" s="1" customFormat="1" ht="24">
+      <c r="A12" s="33"/>
+      <c r="B12" s="34">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="39" t="s">
+      <c r="G12" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="38" t="s">
+      <c r="H12" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="39" t="s">
+      <c r="I12" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="38">
-        <v>1</v>
-      </c>
-      <c r="K12" s="38">
+      <c r="J12" s="36">
+        <v>1</v>
+      </c>
+      <c r="K12" s="36">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L12" s="62"/>
-      <c r="M12" s="38"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A13" s="35"/>
-      <c r="B13" s="36">
+      <c r="L12" s="37"/>
+      <c r="M12" s="36"/>
+    </row>
+    <row r="13" spans="1:13" s="1" customFormat="1">
+      <c r="A13" s="33"/>
+      <c r="B13" s="34">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="E13" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="41" t="s">
+      <c r="G13" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="40" t="s">
+      <c r="H13" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="38">
         <v>2</v>
       </c>
-      <c r="K13" s="40">
+      <c r="K13" s="38">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L13" s="63"/>
-      <c r="M13" s="40"/>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A14" s="35"/>
-      <c r="B14" s="36">
+      <c r="L13" s="37"/>
+      <c r="M13" s="38"/>
+    </row>
+    <row r="14" spans="1:13" s="1" customFormat="1">
+      <c r="A14" s="33"/>
+      <c r="B14" s="34">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="39" t="s">
+      <c r="G14" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="38" t="s">
+      <c r="H14" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="I14" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="J14" s="38">
+      <c r="J14" s="36">
         <v>2</v>
       </c>
-      <c r="K14" s="38">
+      <c r="K14" s="36">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L14" s="62"/>
-      <c r="M14" s="38"/>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="24.75" spans="1:13">
-      <c r="A15" s="35"/>
-      <c r="B15" s="36">
+      <c r="L14" s="37"/>
+      <c r="M14" s="36"/>
+    </row>
+    <row r="15" spans="1:13" s="1" customFormat="1" ht="36">
+      <c r="A15" s="33"/>
+      <c r="B15" s="34">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="D15" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="41" t="s">
+      <c r="G15" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="40" t="s">
+      <c r="H15" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="I15" s="41" t="s">
+      <c r="I15" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="J15" s="40">
-        <v>1</v>
-      </c>
-      <c r="K15" s="40">
+      <c r="J15" s="38">
+        <v>1</v>
+      </c>
+      <c r="K15" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L15" s="63"/>
-      <c r="M15" s="40"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A16" s="35"/>
-      <c r="B16" s="36">
+      <c r="L15" s="37"/>
+      <c r="M15" s="38"/>
+    </row>
+    <row r="16" spans="1:13" s="1" customFormat="1">
+      <c r="A16" s="33"/>
+      <c r="B16" s="34">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="38" t="s">
+      <c r="F16" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="39" t="s">
+      <c r="G16" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="38" t="s">
+      <c r="H16" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="I16" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J16" s="38">
-        <v>1</v>
-      </c>
-      <c r="K16" s="38">
+      <c r="I16" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J16" s="36">
+        <v>1</v>
+      </c>
+      <c r="K16" s="36">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L16" s="62"/>
-      <c r="M16" s="38"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="36.75" spans="1:13">
-      <c r="A17" s="35"/>
-      <c r="B17" s="36">
+      <c r="L16" s="37"/>
+      <c r="M16" s="36"/>
+    </row>
+    <row r="17" spans="1:13" s="1" customFormat="1" ht="48">
+      <c r="A17" s="33"/>
+      <c r="B17" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="D17" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="40" t="s">
+      <c r="H17" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="I17" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J17" s="40">
-        <v>1</v>
-      </c>
-      <c r="K17" s="40">
+      <c r="I17" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J17" s="38">
+        <v>1</v>
+      </c>
+      <c r="K17" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L17" s="63"/>
-      <c r="M17" s="40"/>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A18" s="35"/>
-      <c r="B18" s="36">
+      <c r="L17" s="37"/>
+      <c r="M17" s="38"/>
+    </row>
+    <row r="18" spans="1:13" s="1" customFormat="1">
+      <c r="A18" s="33"/>
+      <c r="B18" s="34">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="G18" s="39" t="s">
+      <c r="G18" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="H18" s="38" t="s">
+      <c r="H18" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="I18" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J18" s="38">
-        <v>1</v>
-      </c>
-      <c r="K18" s="38">
+      <c r="I18" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" s="36">
+        <v>1</v>
+      </c>
+      <c r="K18" s="36">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L18" s="62"/>
-      <c r="M18" s="38"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A19" s="35"/>
-      <c r="B19" s="36">
+      <c r="L18" s="37"/>
+      <c r="M18" s="36"/>
+    </row>
+    <row r="19" spans="1:13" s="1" customFormat="1">
+      <c r="A19" s="33"/>
+      <c r="B19" s="34">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="41" t="s">
+      <c r="E19" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="41" t="s">
+      <c r="G19" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="H19" s="40" t="s">
+      <c r="H19" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="I19" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J19" s="40">
-        <v>1</v>
-      </c>
-      <c r="K19" s="40">
+      <c r="I19" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" s="38">
+        <v>1</v>
+      </c>
+      <c r="K19" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L19" s="63"/>
-      <c r="M19" s="40"/>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="48.75" spans="1:13">
-      <c r="A20" s="35"/>
-      <c r="B20" s="36">
+      <c r="L19" s="37"/>
+      <c r="M19" s="38"/>
+    </row>
+    <row r="20" spans="1:13" s="1" customFormat="1" ht="48">
+      <c r="A20" s="33"/>
+      <c r="B20" s="34">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="39" t="s">
+      <c r="E20" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="38" t="s">
+      <c r="F20" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="38" t="s">
+      <c r="H20" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="I20" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J20" s="38">
+      <c r="I20" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="36">
         <v>3</v>
       </c>
-      <c r="K20" s="38">
+      <c r="K20" s="36">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="L20" s="62"/>
-      <c r="M20" s="38"/>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="36.75" spans="1:13">
-      <c r="A21" s="35"/>
-      <c r="B21" s="36">
+      <c r="L20" s="37"/>
+      <c r="M20" s="36"/>
+    </row>
+    <row r="21" spans="1:13" s="1" customFormat="1" ht="36">
+      <c r="A21" s="33"/>
+      <c r="B21" s="34">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="D21" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="38" t="s">
+      <c r="F21" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="H21" s="40" t="s">
+      <c r="H21" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="I21" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J21" s="40">
-        <v>1</v>
-      </c>
-      <c r="K21" s="40">
+      <c r="I21" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J21" s="38">
+        <v>1</v>
+      </c>
+      <c r="K21" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L21" s="63"/>
-      <c r="M21" s="40"/>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="24.75" spans="1:13">
-      <c r="A22" s="35"/>
-      <c r="B22" s="36">
+      <c r="L21" s="37"/>
+      <c r="M21" s="38"/>
+    </row>
+    <row r="22" spans="1:13" s="1" customFormat="1" ht="24">
+      <c r="A22" s="33"/>
+      <c r="B22" s="34">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="E22" s="39" t="s">
+      <c r="E22" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="F22" s="38" t="s">
+      <c r="F22" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="G22" s="39" t="s">
+      <c r="G22" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="H22" s="38" t="s">
+      <c r="H22" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="I22" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J22" s="38">
+      <c r="I22" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J22" s="36">
         <v>2</v>
       </c>
-      <c r="K22" s="38">
+      <c r="K22" s="36">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L22" s="62"/>
-      <c r="M22" s="38"/>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="28.35" spans="1:13">
-      <c r="A23" s="35"/>
-      <c r="B23" s="36">
+      <c r="L22" s="37"/>
+      <c r="M22" s="36"/>
+    </row>
+    <row r="23" spans="1:13" s="1" customFormat="1" ht="25.5">
+      <c r="A23" s="33"/>
+      <c r="B23" s="34">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="40" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="41" t="s">
+      <c r="E23" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="40" t="s">
+      <c r="F23" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="G23" s="41" t="s">
+      <c r="G23" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="H23" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="I23" s="41" t="s">
+      <c r="H23" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="J23" s="40">
+      <c r="J23" s="38">
         <v>5</v>
       </c>
-      <c r="K23" s="40">
+      <c r="K23" s="38">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="L23" s="63"/>
-      <c r="M23" s="40"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="48.75" spans="1:13">
-      <c r="A24" s="35"/>
-      <c r="B24" s="36">
+      <c r="L23" s="37"/>
+      <c r="M23" s="38"/>
+    </row>
+    <row r="24" spans="1:13" s="1" customFormat="1" ht="48">
+      <c r="A24" s="33"/>
+      <c r="B24" s="34">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="E24" s="37" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="38" t="s">
+      <c r="F24" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G24" s="38" t="s">
+      <c r="G24" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="H24" s="38" t="s">
+      <c r="H24" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="I24" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J24" s="38">
-        <v>1</v>
-      </c>
-      <c r="K24" s="38">
+      <c r="I24" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24" s="36">
+        <v>1</v>
+      </c>
+      <c r="K24" s="36">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L24" s="62"/>
-      <c r="M24" s="38"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="24.75" spans="1:13">
-      <c r="A25" s="35"/>
-      <c r="B25" s="36">
+      <c r="L24" s="37"/>
+      <c r="M24" s="36"/>
+    </row>
+    <row r="25" spans="1:13" s="1" customFormat="1" ht="24">
+      <c r="A25" s="33"/>
+      <c r="B25" s="34">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="40" t="s">
+      <c r="D25" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="E25" s="41" t="s">
+      <c r="E25" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="F25" s="38" t="s">
+      <c r="F25" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G25" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="H25" s="40" t="s">
+      <c r="H25" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="I25" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J25" s="40">
-        <v>1</v>
-      </c>
-      <c r="K25" s="40">
+      <c r="I25" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J25" s="38">
+        <v>1</v>
+      </c>
+      <c r="K25" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L25" s="63"/>
-      <c r="M25" s="40"/>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="24.75" spans="1:13">
-      <c r="A26" s="35"/>
-      <c r="B26" s="36">
+      <c r="L25" s="37"/>
+      <c r="M25" s="38"/>
+    </row>
+    <row r="26" spans="1:13" s="1" customFormat="1" ht="24">
+      <c r="A26" s="33"/>
+      <c r="B26" s="34">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="E26" s="39" t="s">
+      <c r="E26" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G26" s="39" t="s">
+      <c r="G26" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="H26" s="38" t="s">
+      <c r="H26" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="I26" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J26" s="38">
+      <c r="I26" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J26" s="36">
         <v>2</v>
       </c>
-      <c r="K26" s="38">
+      <c r="K26" s="36">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L26" s="62"/>
-      <c r="M26" s="38"/>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="36.75" spans="1:13">
-      <c r="A27" s="35"/>
-      <c r="B27" s="36">
+      <c r="L26" s="37"/>
+      <c r="M26" s="36"/>
+    </row>
+    <row r="27" spans="1:13" s="1" customFormat="1" ht="48">
+      <c r="A27" s="33"/>
+      <c r="B27" s="34">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="40" t="s">
+      <c r="D27" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="41" t="s">
+      <c r="E27" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="40" t="s">
+      <c r="F27" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="G27" s="41" t="s">
+      <c r="G27" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="H27" s="40" t="s">
+      <c r="H27" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="I27" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J27" s="40">
-        <v>1</v>
-      </c>
-      <c r="K27" s="40">
+      <c r="I27" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J27" s="38">
+        <v>1</v>
+      </c>
+      <c r="K27" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L27" s="63"/>
-      <c r="M27" s="40"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A28" s="35"/>
-      <c r="B28" s="36">
+      <c r="L27" s="37"/>
+      <c r="M27" s="38"/>
+    </row>
+    <row r="28" spans="1:13" s="1" customFormat="1">
+      <c r="A28" s="33"/>
+      <c r="B28" s="34">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="D28" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="E28" s="39" t="s">
+      <c r="E28" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="F28" s="38" t="s">
+      <c r="F28" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G28" s="38" t="s">
+      <c r="G28" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="H28" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="I28" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J28" s="38">
+      <c r="H28" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J28" s="36">
         <v>3</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28" s="36">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="L28" s="62"/>
-      <c r="M28" s="38"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="36.75" spans="1:13">
-      <c r="A29" s="35"/>
-      <c r="B29" s="36">
+      <c r="L28" s="37"/>
+      <c r="M28" s="36"/>
+    </row>
+    <row r="29" spans="1:13" s="1" customFormat="1" ht="36">
+      <c r="A29" s="33"/>
+      <c r="B29" s="34">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C29" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D29" s="40" t="s">
+      <c r="D29" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="E29" s="41" t="s">
+      <c r="E29" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="F29" s="40" t="s">
+      <c r="F29" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="G29" s="41" t="s">
+      <c r="G29" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="H29" s="40" t="s">
+      <c r="H29" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="I29" s="41" t="s">
+      <c r="I29" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="J29" s="40">
+      <c r="J29" s="38">
         <v>2</v>
       </c>
-      <c r="K29" s="40">
+      <c r="K29" s="38">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L29" s="63"/>
-      <c r="M29" s="40"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="36.75" spans="1:13">
-      <c r="A30" s="35"/>
-      <c r="B30" s="36">
+      <c r="L29" s="37"/>
+      <c r="M29" s="38"/>
+    </row>
+    <row r="30" spans="1:13" s="1" customFormat="1" ht="36">
+      <c r="A30" s="33"/>
+      <c r="B30" s="34">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="37" t="s">
+      <c r="C30" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="E30" s="39" t="s">
+      <c r="E30" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="F30" s="38" t="s">
+      <c r="F30" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="G30" s="39" t="s">
+      <c r="G30" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="H30" s="38" t="s">
+      <c r="H30" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="I30" s="39" t="s">
+      <c r="I30" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="J30" s="38">
-        <v>1</v>
-      </c>
-      <c r="K30" s="38">
+      <c r="J30" s="36">
+        <v>1</v>
+      </c>
+      <c r="K30" s="36">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L30" s="62"/>
-      <c r="M30" s="38"/>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A31" s="35"/>
-      <c r="B31" s="36">
+      <c r="L30" s="37"/>
+      <c r="M30" s="36"/>
+    </row>
+    <row r="31" spans="1:13" s="1" customFormat="1">
+      <c r="A31" s="33"/>
+      <c r="B31" s="34">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="42" t="s">
+      <c r="C31" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D31" s="40" t="s">
+      <c r="D31" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="E31" s="41" t="s">
+      <c r="E31" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="40" t="s">
+      <c r="F31" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="G31" s="41" t="s">
+      <c r="G31" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="H31" s="40" t="s">
+      <c r="H31" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="41" t="s">
+      <c r="I31" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="J31" s="40">
+      <c r="J31" s="38">
         <v>7</v>
       </c>
-      <c r="K31" s="40">
+      <c r="K31" s="38">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="L31" s="63"/>
-      <c r="M31" s="40"/>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="36.75" spans="1:13">
-      <c r="A32" s="35"/>
-      <c r="B32" s="36">
+      <c r="L31" s="37"/>
+      <c r="M31" s="38"/>
+    </row>
+    <row r="32" spans="1:13" s="1" customFormat="1" ht="36">
+      <c r="A32" s="33"/>
+      <c r="B32" s="34">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="42" t="s">
+      <c r="C32" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D32" s="38" t="s">
+      <c r="D32" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="E32" s="39" t="s">
+      <c r="E32" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="F32" s="38" t="s">
+      <c r="F32" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="G32" s="39" t="s">
+      <c r="G32" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="H32" s="38" t="s">
+      <c r="H32" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="I32" s="39" t="s">
+      <c r="I32" s="37" t="s">
         <v>138</v>
       </c>
-      <c r="J32" s="38">
-        <v>1</v>
-      </c>
-      <c r="K32" s="38">
+      <c r="J32" s="36">
+        <v>1</v>
+      </c>
+      <c r="K32" s="36">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L32" s="62"/>
-      <c r="M32" s="38"/>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A33" s="35"/>
-      <c r="B33" s="36">
+      <c r="L32" s="37"/>
+      <c r="M32" s="36"/>
+    </row>
+    <row r="33" spans="1:13" s="1" customFormat="1">
+      <c r="A33" s="33"/>
+      <c r="B33" s="34">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="42" t="s">
+      <c r="C33" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="40" t="s">
+      <c r="D33" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="E33" s="41" t="s">
+      <c r="E33" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="F33" s="40" t="s">
+      <c r="F33" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="G33" s="41" t="s">
+      <c r="G33" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="H33" s="40" t="s">
+      <c r="H33" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I33" s="41" t="s">
+      <c r="I33" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="J33" s="40">
-        <v>1</v>
-      </c>
-      <c r="K33" s="40">
+      <c r="J33" s="38">
+        <v>1</v>
+      </c>
+      <c r="K33" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L33" s="63"/>
-      <c r="M33" s="40"/>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="36.75" spans="1:13">
-      <c r="A34" s="35"/>
-      <c r="B34" s="36">
+      <c r="L33" s="37"/>
+      <c r="M33" s="38"/>
+    </row>
+    <row r="34" spans="1:13" s="1" customFormat="1" ht="36">
+      <c r="A34" s="33"/>
+      <c r="B34" s="34">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="37" t="s">
+      <c r="C34" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="38" t="s">
+      <c r="D34" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="39" t="s">
+      <c r="E34" s="37" t="s">
         <v>143</v>
       </c>
-      <c r="F34" s="38" t="s">
+      <c r="F34" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="G34" s="39" t="s">
+      <c r="G34" s="37" t="s">
         <v>144</v>
       </c>
-      <c r="H34" s="38" t="s">
+      <c r="H34" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="I34" s="39" t="s">
+      <c r="I34" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="J34" s="38">
-        <v>1</v>
-      </c>
-      <c r="K34" s="38">
+      <c r="J34" s="36">
+        <v>1</v>
+      </c>
+      <c r="K34" s="36">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L34" s="62"/>
-      <c r="M34" s="38"/>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A35" s="35"/>
-      <c r="B35" s="36">
+      <c r="L34" s="37"/>
+      <c r="M34" s="36"/>
+    </row>
+    <row r="35" spans="1:13" s="1" customFormat="1">
+      <c r="A35" s="33"/>
+      <c r="B35" s="34">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="42" t="s">
+      <c r="C35" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="40" t="s">
+      <c r="D35" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="E35" s="41" t="s">
+      <c r="E35" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="F35" s="40" t="s">
+      <c r="F35" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="G35" s="41" t="s">
+      <c r="G35" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="H35" s="40" t="s">
+      <c r="H35" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="I35" s="41" t="s">
+      <c r="I35" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="J35" s="40">
+      <c r="J35" s="38">
         <v>5</v>
       </c>
-      <c r="K35" s="40">
+      <c r="K35" s="38">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="L35" s="63"/>
-      <c r="M35" s="40"/>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A36" s="35"/>
-      <c r="B36" s="36">
+      <c r="L35" s="37"/>
+      <c r="M35" s="38"/>
+    </row>
+    <row r="36" spans="1:13" s="1" customFormat="1">
+      <c r="A36" s="33"/>
+      <c r="B36" s="34">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="37" t="s">
+      <c r="C36" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="D36" s="38" t="s">
+      <c r="D36" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="E36" s="39" t="s">
+      <c r="E36" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="F36" s="38" t="s">
+      <c r="F36" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G36" s="39" t="s">
+      <c r="G36" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="H36" s="38" t="s">
+      <c r="H36" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="I36" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J36" s="38">
-        <v>1</v>
-      </c>
-      <c r="K36" s="38">
+      <c r="I36" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J36" s="36">
+        <v>1</v>
+      </c>
+      <c r="K36" s="36">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L36" s="62"/>
-      <c r="M36" s="38"/>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A37" s="35"/>
-      <c r="B37" s="36">
+      <c r="L36" s="37"/>
+      <c r="M36" s="36"/>
+    </row>
+    <row r="37" spans="1:13" s="1" customFormat="1">
+      <c r="A37" s="33"/>
+      <c r="B37" s="34">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="37" t="s">
+      <c r="C37" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D37" s="40" t="s">
+      <c r="D37" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="E37" s="41" t="s">
+      <c r="E37" s="39" t="s">
         <v>193</v>
       </c>
-      <c r="F37" s="40" t="s">
+      <c r="F37" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="G37" s="41" t="s">
+      <c r="G37" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="H37" s="40" t="s">
+      <c r="H37" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="I37" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J37" s="40">
-        <v>1</v>
-      </c>
-      <c r="K37" s="40">
+      <c r="I37" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J37" s="38">
+        <v>1</v>
+      </c>
+      <c r="K37" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L37" s="63"/>
-      <c r="M37" s="40"/>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A38" s="35"/>
-      <c r="B38" s="36">
+      <c r="L37" s="37"/>
+      <c r="M37" s="38"/>
+    </row>
+    <row r="38" spans="1:13" s="1" customFormat="1" ht="24">
+      <c r="A38" s="33"/>
+      <c r="B38" s="34">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="37" t="s">
+      <c r="C38" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D38" s="38" t="s">
+      <c r="D38" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="E38" s="39" t="s">
+      <c r="E38" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="F38" s="38" t="s">
+      <c r="F38" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="G38" s="39" t="s">
+      <c r="G38" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="H38" s="38" t="s">
+      <c r="H38" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="I38" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J38" s="38">
-        <v>1</v>
-      </c>
-      <c r="K38" s="38">
+      <c r="I38" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J38" s="36">
+        <v>1</v>
+      </c>
+      <c r="K38" s="36">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L38" s="62"/>
-      <c r="M38" s="38"/>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:13">
-      <c r="A39" s="35"/>
-      <c r="B39" s="36">
+      <c r="L38" s="37"/>
+      <c r="M38" s="36"/>
+    </row>
+    <row r="39" spans="1:13" s="1" customFormat="1" ht="24">
+      <c r="A39" s="33"/>
+      <c r="B39" s="34">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="37" t="s">
+      <c r="C39" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D39" s="40" t="s">
+      <c r="D39" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="E39" s="41" t="s">
+      <c r="E39" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="F39" s="40" t="s">
+      <c r="F39" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="G39" s="41" t="s">
+      <c r="G39" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="H39" s="40" t="s">
+      <c r="H39" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="I39" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J39" s="40">
-        <v>1</v>
-      </c>
-      <c r="K39" s="40">
+      <c r="I39" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="J39" s="38">
+        <v>1</v>
+      </c>
+      <c r="K39" s="38">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L39" s="63"/>
-      <c r="M39" s="40"/>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="15.15" spans="1:13">
-      <c r="A40" s="35"/>
-      <c r="B40" s="36">
+      <c r="L39" s="37"/>
+      <c r="M39" s="38"/>
+    </row>
+    <row r="40" spans="1:13" s="1" customFormat="1" ht="24">
+      <c r="A40" s="33"/>
+      <c r="B40" s="34">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="37" t="s">
+      <c r="C40" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="36" t="s">
         <v>172</v>
       </c>
-      <c r="E40" s="39" t="s">
+      <c r="E40" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="F40" s="38" t="s">
+      <c r="F40" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G40" s="38" t="s">
+      <c r="G40" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="H40" s="38" t="s">
+      <c r="H40" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="I40" s="39" t="s">
+      <c r="I40" s="37" t="s">
         <v>176</v>
       </c>
-      <c r="J40" s="38">
-        <v>1</v>
-      </c>
-      <c r="K40" s="38">
+      <c r="J40" s="36">
+        <v>1</v>
+      </c>
+      <c r="K40" s="36">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L40" s="62"/>
-      <c r="M40" s="38"/>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="24.75" spans="1:13">
-      <c r="A41" s="35"/>
-      <c r="B41" s="36">
+      <c r="L40" s="37"/>
+      <c r="M40" s="36"/>
+    </row>
+    <row r="41" spans="1:13" s="1" customFormat="1" ht="24">
+      <c r="A41" s="33"/>
+      <c r="B41" s="34">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="42" t="s">
+      <c r="C41" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="D41" s="40" t="s">
+      <c r="D41" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="E41" s="41" t="s">
+      <c r="E41" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="F41" s="38" t="s">
+      <c r="F41" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G41" s="40" t="s">
+      <c r="G41" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="H41" s="40" t="s">
+      <c r="H41" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="I41" s="41" t="s">
+      <c r="I41" s="39" t="s">
         <v>181</v>
       </c>
-      <c r="J41" s="40">
-        <v>1</v>
-      </c>
-      <c r="K41" s="40">
+      <c r="J41" s="38">
+        <v>1</v>
+      </c>
+      <c r="K41" s="36">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="L41" s="63"/>
-      <c r="M41" s="40"/>
-    </row>
-    <row r="42" customFormat="1" ht="36.75" spans="1:13">
+      <c r="L41" s="37"/>
+      <c r="M41" s="38"/>
+    </row>
+    <row r="42" spans="1:13" ht="48">
       <c r="A42" s="2"/>
-      <c r="B42" s="36">
+      <c r="B42" s="34">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="42" t="s">
+      <c r="C42" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="D42" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="E42" s="41" t="s">
+      <c r="D42" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="F42" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G42" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="H42" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="I42" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="J42" s="40">
-        <v>1</v>
-      </c>
-      <c r="K42" s="40">
-        <f t="shared" ref="K42:K45" si="2">J42*5</f>
-        <v>5</v>
-      </c>
-      <c r="L42" s="64" t="s">
+      <c r="F42" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G42" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="H42" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I42" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="J42" s="38">
+        <v>1</v>
+      </c>
+      <c r="K42" s="36">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L42" s="54" t="s">
         <v>184</v>
       </c>
-      <c r="M42" s="40"/>
-    </row>
-    <row r="43" customFormat="1" ht="15.15" spans="1:13">
+      <c r="M42" s="38"/>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="2"/>
-      <c r="B43" s="36">
+      <c r="B43" s="34">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="C43" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="D43" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" s="41" t="s">
+      <c r="D43" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="F43" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G43" s="40" t="s">
+      <c r="F43" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="H43" s="40" t="s">
+      <c r="H43" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="I43" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="J43" s="40">
-        <v>1</v>
-      </c>
-      <c r="K43" s="40">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L43" s="64" t="s">
+      <c r="I43" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="J43" s="38">
+        <v>1</v>
+      </c>
+      <c r="K43" s="36">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L43" s="54" t="s">
         <v>188</v>
       </c>
-      <c r="M43" s="40"/>
-    </row>
-    <row r="44" customFormat="1" ht="15.15" spans="1:13">
+      <c r="M43" s="38"/>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="2"/>
-      <c r="B44" s="36">
+      <c r="B44" s="34">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="42" t="s">
+      <c r="C44" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="D44" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="41" t="s">
+      <c r="D44" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E44" s="39" t="s">
         <v>189</v>
       </c>
-      <c r="F44" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G44" s="40" t="s">
+      <c r="F44" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G44" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="H44" s="40" t="s">
+      <c r="H44" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="I44" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="J44" s="40">
-        <v>1</v>
-      </c>
-      <c r="K44" s="40">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L44" s="64" t="s">
+      <c r="I44" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="J44" s="38">
+        <v>1</v>
+      </c>
+      <c r="K44" s="36">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L44" s="54" t="s">
         <v>188</v>
       </c>
-      <c r="M44" s="40"/>
-    </row>
-    <row r="45" customFormat="1" ht="48.75" spans="1:13">
+      <c r="M44" s="38"/>
+    </row>
+    <row r="45" spans="1:13" ht="48">
       <c r="A45" s="2"/>
-      <c r="B45" s="36">
+      <c r="B45" s="34">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="D45" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="E45" s="41" t="s">
+      <c r="D45" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E45" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="F45" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G45" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="H45" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="I45" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="J45" s="40">
-        <v>1</v>
-      </c>
-      <c r="K45" s="40">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L45" s="64" t="s">
+      <c r="F45" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="G45" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="H45" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I45" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="J45" s="38">
+        <v>1</v>
+      </c>
+      <c r="K45" s="36">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L45" s="54" t="s">
         <v>184</v>
       </c>
-      <c r="M45" s="40"/>
+      <c r="M45" s="38"/>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="2"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="47"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="48"/>
-      <c r="K46" s="48"/>
-      <c r="L46" s="65"/>
-      <c r="M46" s="66"/>
-    </row>
-    <row r="47" ht="15.15" spans="1:13">
+      <c r="B46" s="41"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="46"/>
+      <c r="K46" s="46"/>
+      <c r="L46" s="46"/>
+      <c r="M46" s="55"/>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="2"/>
-      <c r="B47" s="49"/>
-      <c r="C47" s="50"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="52"/>
-      <c r="H47" s="52"/>
-      <c r="I47" s="52"/>
-      <c r="J47" s="52"/>
-      <c r="K47" s="52"/>
-      <c r="L47" s="67"/>
-      <c r="M47" s="68"/>
+      <c r="B47" s="47"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="50"/>
+      <c r="G47" s="50"/>
+      <c r="H47" s="50"/>
+      <c r="I47" s="50"/>
+      <c r="J47" s="50"/>
+      <c r="K47" s="50"/>
+      <c r="L47" s="50"/>
+      <c r="M47" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5323,13 +4718,12 @@
     <mergeCell ref="M3:M8"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="L42" r:id="rId2" display="Aliexpress"/>
-    <hyperlink ref="L43" r:id="rId3" display="LCSC"/>
-    <hyperlink ref="L44" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="L45" r:id="rId5" display="Aliexpress"/>
+    <hyperlink ref="L42" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="L43" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="L44" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="L45" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>